--- a/project/HW4/22127435/22127435_GUI_Checklist.xlsx
+++ b/project/HW4/22127435/22127435_GUI_Checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viett\OneDrive\Documents\GitHub\Testing-PRJ-SM\project\HW4\22127435\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C0EDEA-B917-4EA5-B470-10689506A8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13300B8F-FF66-4EB8-908D-770B9971548E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GUI list" sheetId="1" r:id="rId1"/>
@@ -259,9 +259,6 @@
     <t>Có lỗi hiển thị logic nội dung không?</t>
   </si>
   <si>
-    <t>- Hiển thị filter sai: lọc Name (A - Z) nhưng mà hiển thị (Z - A) và ngược lại; lọc Price (High - Low) mà hiển thị (Low - High) và ngược lại</t>
-  </si>
-  <si>
     <t>HÌNH ẢNH</t>
   </si>
   <si>
@@ -500,6 +497,10 @@
   </si>
   <si>
     <t>3.1.4</t>
+  </si>
+  <si>
+    <t>Hiển thị filter sai: lọc Name (A - Z) nhưng mà hiển thị (Z - A) và ngược lại; lọc Price (High - Low) mà hiển thị (Low - High) và ngược lại
+Tên người dùng không hiển thị được, thay vào đó lại hiển thị "User Data Not Found"</t>
   </si>
 </sst>
 </file>
@@ -600,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -690,11 +691,46 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -808,38 +844,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFB8CCE4"/>
           <bgColor rgb="FFB8CCE4"/>
         </patternFill>
@@ -924,15 +928,15 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A4:I79" headerRowCount="0">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Column1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Column2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Column3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Column4" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Column5" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Column6" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Column7" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Column8" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Column9" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Column1" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Column2" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Column3" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Column4" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Column5" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Column6" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Column7" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Column8" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Column9" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="GUI (1)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -2451,7 +2455,7 @@
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="29" t="s">
         <v>23</v>
       </c>
@@ -2468,7 +2472,7 @@
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
     </row>
-    <row r="11" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="29" t="s">
         <v>25</v>
       </c>
@@ -2583,7 +2587,7 @@
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
     </row>
-    <row r="17" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="29" t="s">
         <v>36</v>
       </c>
@@ -2923,8 +2927,8 @@
       <c r="H35" s="13"/>
       <c r="I35" s="13"/>
     </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="29" t="s">
+    <row r="36" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="43" t="s">
         <v>75</v>
       </c>
       <c r="B36" s="33" t="s">
@@ -2934,8 +2938,8 @@
       <c r="D36" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="33" t="s">
-        <v>77</v>
+      <c r="E36" s="39" t="s">
+        <v>157</v>
       </c>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
@@ -2947,7 +2951,7 @@
         <v>1.4</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
@@ -2976,10 +2980,10 @@
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="30" t="s">
         <v>79</v>
-      </c>
-      <c r="B38" s="30" t="s">
-        <v>80</v>
       </c>
       <c r="C38" s="31" t="s">
         <v>16</v>
@@ -2993,10 +2997,10 @@
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="30" t="s">
         <v>81</v>
-      </c>
-      <c r="B39" s="30" t="s">
-        <v>82</v>
       </c>
       <c r="C39" s="31" t="s">
         <v>16</v>
@@ -3010,10 +3014,10 @@
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="30" t="s">
         <v>83</v>
-      </c>
-      <c r="B40" s="30" t="s">
-        <v>84</v>
       </c>
       <c r="C40" s="31" t="s">
         <v>16</v>
@@ -3027,10 +3031,10 @@
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="30" t="s">
         <v>85</v>
-      </c>
-      <c r="B41" s="30" t="s">
-        <v>86</v>
       </c>
       <c r="C41" s="31" t="s">
         <v>16</v>
@@ -3044,10 +3048,10 @@
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="30" t="s">
         <v>87</v>
-      </c>
-      <c r="B42" s="30" t="s">
-        <v>88</v>
       </c>
       <c r="C42" s="31" t="s">
         <v>16</v>
@@ -3061,10 +3065,10 @@
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="30" t="s">
         <v>89</v>
-      </c>
-      <c r="B43" s="30" t="s">
-        <v>90</v>
       </c>
       <c r="C43" s="31" t="s">
         <v>16</v>
@@ -3078,10 +3082,10 @@
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="30" t="s">
         <v>91</v>
-      </c>
-      <c r="B44" s="30" t="s">
-        <v>92</v>
       </c>
       <c r="C44" s="31" t="s">
         <v>16</v>
@@ -3098,7 +3102,7 @@
         <v>1.5</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C45" s="31"/>
       <c r="D45" s="31"/>
@@ -3127,10 +3131,10 @@
     </row>
     <row r="46" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" s="37" t="s">
         <v>94</v>
-      </c>
-      <c r="B46" s="37" t="s">
-        <v>95</v>
       </c>
       <c r="C46" s="22"/>
       <c r="D46" s="22"/>
@@ -3159,10 +3163,10 @@
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="B47" s="39" t="s">
         <v>96</v>
-      </c>
-      <c r="B47" s="39" t="s">
-        <v>97</v>
       </c>
       <c r="C47" s="31" t="s">
         <v>16</v>
@@ -3176,10 +3180,10 @@
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="30" t="s">
         <v>98</v>
-      </c>
-      <c r="B48" s="30" t="s">
-        <v>99</v>
       </c>
       <c r="C48" s="31" t="s">
         <v>16</v>
@@ -3193,10 +3197,10 @@
     </row>
     <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" s="39" t="s">
         <v>100</v>
-      </c>
-      <c r="B49" s="39" t="s">
-        <v>101</v>
       </c>
       <c r="C49" s="31" t="s">
         <v>16</v>
@@ -3210,10 +3214,10 @@
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="39" t="s">
         <v>102</v>
-      </c>
-      <c r="B50" s="39" t="s">
-        <v>103</v>
       </c>
       <c r="C50" s="31" t="s">
         <v>16</v>
@@ -3227,10 +3231,10 @@
     </row>
     <row r="51" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" s="21" t="s">
         <v>104</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>105</v>
       </c>
       <c r="C51" s="22"/>
       <c r="D51" s="22"/>
@@ -3259,10 +3263,10 @@
     </row>
     <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" s="30" t="s">
         <v>106</v>
-      </c>
-      <c r="B52" s="30" t="s">
-        <v>107</v>
       </c>
       <c r="C52" s="31" t="s">
         <v>16</v>
@@ -3276,10 +3280,10 @@
     </row>
     <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53" s="21" t="s">
         <v>108</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>109</v>
       </c>
       <c r="C53" s="31"/>
       <c r="D53" s="31"/>
@@ -3291,10 +3295,10 @@
     </row>
     <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" s="30" t="s">
         <v>110</v>
-      </c>
-      <c r="B54" s="30" t="s">
-        <v>111</v>
       </c>
       <c r="C54" s="31"/>
       <c r="D54" s="31" t="s">
@@ -3308,10 +3312,10 @@
     </row>
     <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" s="30" t="s">
         <v>112</v>
-      </c>
-      <c r="B55" s="30" t="s">
-        <v>113</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>16</v>
@@ -3328,7 +3332,7 @@
         <v>2</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C56" s="40"/>
       <c r="D56" s="40"/>
@@ -3360,7 +3364,7 @@
         <v>2.1</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C57" s="22"/>
       <c r="D57" s="22"/>
@@ -3389,10 +3393,10 @@
     </row>
     <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="30" t="s">
         <v>116</v>
-      </c>
-      <c r="B58" s="30" t="s">
-        <v>117</v>
       </c>
       <c r="C58" s="31" t="s">
         <v>16</v>
@@ -3406,10 +3410,10 @@
     </row>
     <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" s="30" t="s">
         <v>118</v>
-      </c>
-      <c r="B59" s="30" t="s">
-        <v>119</v>
       </c>
       <c r="C59" s="31" t="s">
         <v>16</v>
@@ -3423,10 +3427,10 @@
     </row>
     <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" s="30" t="s">
         <v>120</v>
-      </c>
-      <c r="B60" s="30" t="s">
-        <v>121</v>
       </c>
       <c r="C60" s="31" t="s">
         <v>16</v>
@@ -3440,10 +3444,10 @@
     </row>
     <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" s="30" t="s">
         <v>122</v>
-      </c>
-      <c r="B61" s="30" t="s">
-        <v>123</v>
       </c>
       <c r="C61" s="31"/>
       <c r="D61" s="31" t="s">
@@ -3457,10 +3461,10 @@
     </row>
     <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="B62" s="30" t="s">
         <v>124</v>
-      </c>
-      <c r="B62" s="30" t="s">
-        <v>125</v>
       </c>
       <c r="C62" s="31" t="s">
         <v>16</v>
@@ -3477,7 +3481,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C63" s="22"/>
       <c r="D63" s="22"/>
@@ -3506,10 +3510,10 @@
     </row>
     <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="30" t="s">
         <v>127</v>
-      </c>
-      <c r="B64" s="30" t="s">
-        <v>128</v>
       </c>
       <c r="C64" s="31" t="s">
         <v>16</v>
@@ -3523,10 +3527,10 @@
     </row>
     <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" s="30" t="s">
         <v>129</v>
-      </c>
-      <c r="B65" s="30" t="s">
-        <v>130</v>
       </c>
       <c r="C65" s="31" t="s">
         <v>16</v>
@@ -3540,10 +3544,10 @@
     </row>
     <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" s="30" t="s">
         <v>131</v>
-      </c>
-      <c r="B66" s="30" t="s">
-        <v>132</v>
       </c>
       <c r="C66" s="31" t="s">
         <v>16</v>
@@ -3557,17 +3561,17 @@
     </row>
     <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" s="30" t="s">
         <v>133</v>
-      </c>
-      <c r="B67" s="30" t="s">
-        <v>134</v>
       </c>
       <c r="C67" s="31" t="s">
         <v>16</v>
       </c>
       <c r="D67" s="31"/>
       <c r="E67" s="32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F67" s="13"/>
       <c r="G67" s="13"/>
@@ -3576,10 +3580,10 @@
     </row>
     <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" s="30" t="s">
         <v>136</v>
-      </c>
-      <c r="B68" s="30" t="s">
-        <v>137</v>
       </c>
       <c r="C68" s="31"/>
       <c r="D68" s="31" t="s">
@@ -3593,10 +3597,10 @@
     </row>
     <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" s="39" t="s">
         <v>138</v>
-      </c>
-      <c r="B69" s="39" t="s">
-        <v>139</v>
       </c>
       <c r="C69" s="31"/>
       <c r="D69" s="31" t="s">
@@ -3610,10 +3614,10 @@
     </row>
     <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B70" s="30" t="s">
         <v>140</v>
-      </c>
-      <c r="B70" s="30" t="s">
-        <v>141</v>
       </c>
       <c r="C70" s="31" t="s">
         <v>16</v>
@@ -3627,10 +3631,10 @@
     </row>
     <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B71" s="30" t="s">
         <v>142</v>
-      </c>
-      <c r="B71" s="30" t="s">
-        <v>143</v>
       </c>
       <c r="C71" s="31"/>
       <c r="D71" s="31" t="s">
@@ -3644,10 +3648,10 @@
     </row>
     <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="30" t="s">
         <v>144</v>
-      </c>
-      <c r="B72" s="30" t="s">
-        <v>145</v>
       </c>
       <c r="C72" s="31"/>
       <c r="D72" s="31" t="s">
@@ -3661,10 +3665,10 @@
     </row>
     <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" s="30" t="s">
         <v>146</v>
-      </c>
-      <c r="B73" s="30" t="s">
-        <v>147</v>
       </c>
       <c r="C73" s="31"/>
       <c r="D73" s="31" t="s">
@@ -3681,7 +3685,7 @@
         <v>3</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C74" s="22"/>
       <c r="D74" s="22"/>
@@ -3713,7 +3717,7 @@
         <v>3.1</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C75" s="22"/>
       <c r="D75" s="22"/>
@@ -3742,10 +3746,10 @@
     </row>
     <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="30" t="s">
         <v>150</v>
-      </c>
-      <c r="B76" s="30" t="s">
-        <v>151</v>
       </c>
       <c r="C76" s="31" t="s">
         <v>16</v>
@@ -3759,10 +3763,10 @@
     </row>
     <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" s="30" t="s">
         <v>152</v>
-      </c>
-      <c r="B77" s="30" t="s">
-        <v>153</v>
       </c>
       <c r="C77" s="31" t="s">
         <v>16</v>
@@ -3776,10 +3780,10 @@
     </row>
     <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" s="30" t="s">
         <v>154</v>
-      </c>
-      <c r="B78" s="30" t="s">
-        <v>155</v>
       </c>
       <c r="C78" s="31" t="s">
         <v>16</v>
@@ -3793,10 +3797,10 @@
     </row>
     <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="42" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C79" s="31" t="s">
         <v>16</v>
